--- a/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>לורן נוימן – בעולם הבא</v>
+        <v>שחר אדמוני - כוכבים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%95%d7%a8%d7%9f-%d7%a0%d7%95%d7%99%d7%9e%d7%9f-%d7%91%d7%a2%d7%95%d7%9c%d7%9d-%d7%94%d7%91%d7%90/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409835&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-01</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "בעולם הבא” של לורן נוימן הוא שיר אבל אינטימי ושקט, כזה שאינו מתפרץ בכאב אלא מחזיק אותו בעדינות. המלנכוליה שבו אינה שוברת – היא מחזקת. במקום דרמה או זעקה, נוימן בוחרת בטון געגועים רך, כמעט לוחש, שמעניק למוות משמעות</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,354 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>לורן נוימן – בעולם הבא</v>
+        <v>שחר אדמוני - כוכבים</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שולי בן - שיר עצוב</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409834&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שולי בן - שיר עצוב</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נוי מיהלי - כולם ישנים</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409833&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נוי מיהלי - כולם ישנים</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מקהלת משאלות - יתגשמו משאלות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409832&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מקהלת משאלות - יתגשמו משאלות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מני ממטרה &amp; דנה בנדנה - מסיבת פורים מטורפת 2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409831&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מני ממטרה &amp; דנה בנדנה - מסיבת פורים מטורפת 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מוטי עויזר - מחרוזת פורים 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409830&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מוטי עויזר - מחרוזת פורים 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ישי שין - חידושים</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409829&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ישי שין - חידושים</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יהנותן לוי - להעריך</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409828&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יהנותן לוי - להעריך</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>חיים באינסאי - מיאמור</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409827&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>חיים באינסאי - מיאמור</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אורי דהן - מכתבים שרופים</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409826&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אורי דהן - מכתבים שרופים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר אדמוני - כוכבים</v>
+        <v>שוקי סלומון &amp; שימי יונייב &amp; אייל טויטו - פורים פארטי 2 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409835&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409850&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שחר אדמוני - כוכבים</v>
+        <v>שוקי סלומון &amp; שימי יונייב &amp; אייל טויטו - פורים פארטי 2 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שולי בן - שיר עצוב</v>
+        <v>נתנאל - עושה שלום</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409834&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409849&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שולי בן - שיר עצוב</v>
+        <v>נתנאל - עושה שלום</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נוי מיהלי - כולם ישנים</v>
+        <v>שירן מור - מחרוזת שמחה באמונה 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409833&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409848&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נוי מיהלי - כולם ישנים</v>
+        <v>שירן מור - מחרוזת שמחה באמונה 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מקהלת משאלות - יתגשמו משאלות</v>
+        <v>רועי סנדלר - לכה דודי</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409832&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409847&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מקהלת משאלות - יתגשמו משאלות</v>
+        <v>רועי סנדלר - לכה דודי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מני ממטרה &amp; דנה בנדנה - מסיבת פורים מטורפת 2026</v>
+        <v>ראובן המלאך - ילדים בודדים קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409831&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409846&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מני ממטרה &amp; דנה בנדנה - מסיבת פורים מטורפת 2026</v>
+        <v>ראובן המלאך - ילדים בודדים קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מוטי עויזר - מחרוזת פורים 2026</v>
+        <v>קלימה - אבא תן לי סימן</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409830&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409845&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מוטי עויזר - מחרוזת פורים 2026</v>
+        <v>קלימה - אבא תן לי סימן</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ישי שין - חידושים</v>
+        <v>פנינה רוזנבלום &amp; אורן כהן - שאגת הארי</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409829&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409844&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ישי שין - חידושים</v>
+        <v>פנינה רוזנבלום &amp; אורן כהן - שאגת הארי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>יהנותן לוי - להעריך</v>
+        <v>נתלי - השטן לובשת פראדה</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409828&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409843&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>יהנותן לוי - להעריך</v>
+        <v>נתלי - השטן לובשת פראדה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>חיים באינסאי - מיאמור</v>
+        <v>ירדן אזולאי - סגרת לי את הדלת</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409827&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409842&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>חיים באינסאי - מיאמור</v>
+        <v>ירדן אזולאי - סגרת לי את הדלת</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אורי דהן - מכתבים שרופים</v>
+        <v>יוסף מויאל - שאגת הארי</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409826&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409841&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,12 +811,202 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אורי דהן - מכתבים שרופים</v>
+        <v>יוסף מויאל - שאגת הארי</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>יובל קונסטנטיני - לא שלך</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409840&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>יובל קונסטנטיני - לא שלך</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>יגל יובל שרעבי - נוביה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409839&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>יגל יובל שרעבי - נוביה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>יגל יובל שרעבי - מכה על חטא</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409838&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>יגל יובל שרעבי - מכה על חטא</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אליה נרקיס - מים מתוקים</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409837&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אליה נרקיס - מים מתוקים</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אליה דרעי - יש אחד</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409836&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אליה דרעי - יש אחד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל לוי – מדויק</v>
+        <v>משה פרץ – יש על מי לסמוך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%9c%d7%95%d7%99-%d7%9e%d7%93%d7%95%d7%99%d7%a7/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%a4%d7%a8%d7%a5-%d7%99%d7%a9-%d7%a2%d7%9c-%d7%9e%d7%99-%d7%9c%d7%a1%d7%9e%d7%95%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-03</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "מדויק” של כוכב הנוער והטיקטוק אייל לוי מייצג היטב את דור הפופ החדש,  שנולד קודם ברשתות החברתיות ורק אחר כך במוזיקה עצמה. זהו שיר שנבנה מראש לעולם של קליפים צעירים, ריקודי דאנס ואתגרי טיקטוק — ופחות להאזנה מסורתית לאלבום</v>
+        <v>השיר מציג שילוב בין שיר אמונה אישי לבין שיר הילולה קצבי המיועד לרחבת הריקודים. משה פרץ מנסה להחזיק שני עולמות במקביל: רוחניות פנימית לצד אנרגיה קהילתית חגיגית. לב השיר נמצא במשפט "לא הכל בידיים שלי / לא הכל צריך תשובה”.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל לוי – מדויק</v>
+        <v>משה פרץ – יש על מי לסמוך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה פרץ – יש על מי לסמוך</v>
+        <v>תהילה זיאמר - הכל מסיבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%a4%d7%a8%d7%a5-%d7%99%d7%a9-%d7%a2%d7%9c-%d7%9e%d7%99-%d7%9c%d7%a1%d7%9e%d7%95%d7%9a/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409868&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר מציג שילוב בין שיר אמונה אישי לבין שיר הילולה קצבי המיועד לרחבת הריקודים. משה פרץ מנסה להחזיק שני עולמות במקביל: רוחניות פנימית לצד אנרגיה קהילתית חגיגית. לב השיר נמצא במשפט "לא הכל בידיים שלי / לא הכל צריך תשובה”.</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,354 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה פרץ – יש על מי לסמוך</v>
+        <v>תהילה זיאמר - הכל מסיבה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שגב בן נעים - השמש איחרה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409867&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שגב בן נעים - השמש איחרה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נתנאל אברהם - מחרוזת כורדית 2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409866&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נתנאל אברהם - מחרוזת כורדית 2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>משה פרץ - יש על מי לסמוך</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409865&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>משה פרץ - יש על מי לסמוך</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>טלי רבקה סימן טוב - הסוד</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409864&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>טלי רבקה סימן טוב - הסוד</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>הירושלמים - עוד אתה איתי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409863&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>הירושלמים - עוד אתה איתי</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דודו קדוש - מחרוזת בא לשכונה בחור חדש 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409862&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דודו קדוש - מחרוזת בא לשכונה בחור חדש 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אורן כדורי - את אמיתית</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409861&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אורן כדורי - את אמיתית</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אור עמרמי ברוקמן - תמיד חוזר למנגינה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409860&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אור עמרמי ברוקמן - תמיד חוזר למנגינה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אדל חן - קומי אורי</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409859&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אדל חן - קומי אורי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תהילה זיאמר - הכל מסיבה</v>
+        <v>יהונתן לוי להעריך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409868&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
+        <v>https://yosmusic.com/%d7%99%d7%94%d7%95%d7%a0%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%9c%d7%94%d7%a2%d7%a8%d7%99%d7%9a/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר “להעריך” של יהונתן לוי הוא בלדה איטית בעלת אופי רגשי, שנשענת על מסורת של שירה מזרחית עם סלסולים ומטען רוחני-אישי. מבחינת תוכן הוא שייך לז’אנר של שירי העצמה אישית ואמונה. הוא נכתב בשפה ישירה מאוד, כמעט דיבורית, ולכן נוצרת תחושה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,354 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תהילה זיאמר - הכל מסיבה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שגב בן נעים - השמש איחרה</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409867&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שגב בן נעים - השמש איחרה</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נתנאל אברהם - מחרוזת כורדית 2026</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409866&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נתנאל אברהם - מחרוזת כורדית 2026</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>משה פרץ - יש על מי לסמוך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409865&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>משה פרץ - יש על מי לסמוך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>טלי רבקה סימן טוב - הסוד</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409864&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>טלי רבקה סימן טוב - הסוד</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>הירושלמים - עוד אתה איתי</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409863&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>הירושלמים - עוד אתה איתי</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>דודו קדוש - מחרוזת בא לשכונה בחור חדש 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409862&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>דודו קדוש - מחרוזת בא לשכונה בחור חדש 2026</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אורן כדורי - את אמיתית</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409861&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אורן כדורי - את אמיתית</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אור עמרמי ברוקמן - תמיד חוזר למנגינה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409860&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אור עמרמי ברוקמן - תמיד חוזר למנגינה</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אדל חן - קומי אורי</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409859&amp;sid=77ba5b981cc516ccd753dc03859fed5a</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אדל חן - קומי אורי</v>
+        <v>יהונתן לוי להעריך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יהונתן לוי להעריך</v>
+        <v>יהונתן לוי – להעריך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-05</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יהונתן לוי להעריך</v>
+        <v>יהונתן לוי – להעריך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יהונתן לוי – להעריך</v>
+        <v>פרחי ירושלים &amp; עמירן דביר - ביי ביי חמינאי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%94%d7%95%d7%a0%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%9c%d7%94%d7%a2%d7%a8%d7%99%d7%9a/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409887&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “להעריך” של יהונתן לוי הוא בלדה איטית בעלת אופי רגשי, שנשענת על מסורת של שירה מזרחית עם סלסולים ומטען רוחני-אישי. מבחינת תוכן הוא שייך לז’אנר של שירי העצמה אישית ואמונה. הוא נכתב בשפה ישירה מאוד, כמעט דיבורית, ולכן נוצרת תחושה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,696 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יהונתן לוי – להעריך</v>
+        <v>פרחי ירושלים &amp; עמירן דביר - ביי ביי חמינאי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אלחנן משמרתי - על משמרתי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409886&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אלחנן משמרתי - על משמרתי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שרוליק מנדלסון &amp; יענקי היל - שחרר לי את כל החסמים</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409885&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שרוליק מנדלסון &amp; יענקי היל - שחרר לי את כל החסמים</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שנאל אלקיים - אל תבוא ואל תגיד לי</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409884&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שנאל אלקיים - אל תבוא ואל תגיד לי</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>שי לסרי - לא כמו פעם קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409883&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>שי לסרי - לא כמו פעם קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>פרחי ירושלים - אהבת השם</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409882&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>פרחי ירושלים - אהבת השם</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>עמי כהן &amp; גדולי הזמר - מחרוזת פורים עמישתה 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409881&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>עמי כהן &amp; גדולי הזמר - מחרוזת פורים עמישתה 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>עידו כנפי - רגשות מעורבים</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409880&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>עידו כנפי - רגשות מעורבים</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>מצדה - תמיד שלך קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409879&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>מצדה - תמיד שלך קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יהונתן פרץ - תחינתי שמעה יה אל</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409878&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יהונתן פרץ - תחינתי שמעה יה אל</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>טל מוסרי &amp; בתאל צברי - נשימה עושה קסמים</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409877&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>טל מוסרי &amp; בתאל צברי - נשימה עושה קסמים</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דיג'יי מאוריקו &amp; בצלאל שמיר - מחרוזת פורים 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409876&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דיג'יי מאוריקו &amp; בצלאל שמיר - מחרוזת פורים 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>דני נגוסו - תקופה כזאת</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409875&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>דני נגוסו - תקופה כזאת</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>דולב הרץ - שלם</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409874&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>דולב הרץ - שלם</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>ברק מזרחי - כמו סם שממכר</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409873&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>ברק מזרחי - כמו סם שממכר</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אלון מיכאל - מחרוזת נשמה 2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409872&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אלון מיכאל - מחרוזת נשמה 2026</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אדרת - היו לילות</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409871&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אדרת - היו לילות</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>אביגיל - לגדול</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409870&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>אביגיל - לגדול</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>אבי חיימי - חיכיתי לך</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409869&amp;sid=13f1d35c30bdb1d886ab819b05e33daf</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>אבי חיימי - חיכיתי לך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
   </ignoredErrors>
 </worksheet>
 </file>